--- a/data/excel/salarios_real.xlsx
+++ b/data/excel/salarios_real.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6187,6 +6187,56 @@
       </c>
       <c r="P117" t="n">
         <v>1.759954730279589</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B118" t="n">
+        <v>82.75510016237175</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.153473703979424</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-2.337137858233429</v>
+      </c>
+      <c r="E118" t="n">
+        <v>67.66830939027427</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.5909916456618092</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-2.421798146425269</v>
+      </c>
+      <c r="H118" t="n">
+        <v>77.11949547625166</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.9685024714637613</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-2.364887360614076</v>
+      </c>
+      <c r="K118" t="n">
+        <v>97.7907373977805</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1.31738094832472</v>
+      </c>
+      <c r="M118" t="n">
+        <v>16.3350655577001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>81.2392286372486</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1.051940221053482</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1.551179880172615</v>
       </c>
     </row>
   </sheetData>
@@ -6259,7 +6309,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T18:11:14Z</t>
+          <t>2026-10-21T19:38:26Z</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6321,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
